--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -36915,12 +36915,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36954,81 +36954,100 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1166</v>
+        <v>209</v>
       </c>
       <c r="O203" t="n">
-        <v>1166</v>
+        <v>209</v>
       </c>
       <c r="R203" t="n">
-        <v>0.3340634462809103</v>
+        <v>1.953080009511219</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37055,17 +37074,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37090,7 +37109,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -37099,26 +37118,103 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="O204" t="n">
-        <v>25</v>
-      </c>
-      <c r="P204" t="n">
-        <v>25</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.4233164387742618</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>209</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -37127,7 +37223,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -37135,9 +37231,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT204" t="n">
@@ -37145,47 +37246,47 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37212,17 +37313,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37247,7 +37348,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -37256,173 +37357,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>25</v>
+        <v>1166</v>
       </c>
       <c r="O205" t="n">
-        <v>25</v>
-      </c>
-      <c r="P205" t="n">
-        <v>25</v>
-      </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
+        <v>1166</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.3340634462809103</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37454,12 +37463,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37484,7 +37493,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -37493,81 +37502,93 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1060</v>
+        <v>25</v>
       </c>
       <c r="O206" t="n">
-        <v>1060</v>
+        <v>25</v>
+      </c>
+      <c r="P206" t="n">
+        <v>25</v>
       </c>
       <c r="R206" t="n">
-        <v>0.3036940420735548</v>
+        <v>0.4233164387742618</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37594,7 +37615,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -37629,7 +37650,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37646,18 +37667,98 @@
       <c r="P207" t="n">
         <v>25</v>
       </c>
-      <c r="R207" t="n">
-        <v>0.4233164387742618</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -37751,17 +37852,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37786,7 +37887,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -37795,173 +37896,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>25</v>
+        <v>1060</v>
       </c>
       <c r="O208" t="n">
-        <v>25</v>
-      </c>
-      <c r="P208" t="n">
-        <v>25</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
+        <v>1060</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.3036940420735548</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37993,12 +38002,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38023,7 +38032,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -38032,81 +38041,93 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>1056</v>
+        <v>25</v>
       </c>
       <c r="O209" t="n">
-        <v>1056</v>
+        <v>25</v>
+      </c>
+      <c r="P209" t="n">
+        <v>25</v>
       </c>
       <c r="R209" t="n">
-        <v>0.3025480268204471</v>
+        <v>0.4233164387742618</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38133,7 +38154,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -38168,7 +38189,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -38177,26 +38198,106 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O210" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P210" t="n">
-        <v>28</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.4741144114271733</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>25</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -38290,17 +38391,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38325,7 +38426,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -38334,173 +38435,81 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>28</v>
+        <v>1056</v>
       </c>
       <c r="O211" t="n">
-        <v>28</v>
-      </c>
-      <c r="P211" t="n">
-        <v>28</v>
-      </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
+        <v>1056</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.3025480268204471</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38532,12 +38541,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38562,7 +38571,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -38571,81 +38580,93 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>993</v>
+        <v>28</v>
       </c>
       <c r="O212" t="n">
-        <v>993</v>
+        <v>28</v>
+      </c>
+      <c r="P212" t="n">
+        <v>28</v>
       </c>
       <c r="R212" t="n">
-        <v>0.2844982865839999</v>
+        <v>0.4741144114271733</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38672,7 +38693,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -38707,7 +38728,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -38716,26 +38737,106 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O213" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P213" t="n">
-        <v>30</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0.5079797265291142</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>28</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -38829,17 +38930,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38864,7 +38965,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -38873,173 +38974,81 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>30</v>
+        <v>993</v>
       </c>
       <c r="O214" t="n">
-        <v>30</v>
-      </c>
-      <c r="P214" t="n">
-        <v>30</v>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
+        <v>993</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.2844982865839999</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39071,12 +39080,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39101,7 +39110,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39110,81 +39119,93 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>1047</v>
+        <v>30</v>
       </c>
       <c r="O215" t="n">
-        <v>1047</v>
+        <v>30</v>
+      </c>
+      <c r="P215" t="n">
+        <v>30</v>
       </c>
       <c r="R215" t="n">
-        <v>0.2999694925009547</v>
+        <v>0.5079797265291142</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39211,17 +39232,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39246,90 +39267,182 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O216" t="n">
-        <v>26</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0.09549310730751455</v>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="P216" t="n">
+        <v>30</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39361,12 +39474,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39391,109 +39504,90 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>1047</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
+        <v>1047</v>
       </c>
       <c r="R217" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.2999694925009547</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39520,17 +39614,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39564,175 +39658,81 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O218" t="n">
-        <v>1</v>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.09549310730751455</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN218" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP218" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT218" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV218" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39764,12 +39764,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39803,13 +39803,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R219" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -39838,7 +39838,7 @@
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
@@ -39848,7 +39848,7 @@
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -39856,47 +39856,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39928,12 +39928,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39967,29 +39967,29 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -40014,7 +40014,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -40049,17 +40049,17 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
@@ -40087,7 +40087,7 @@
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -40095,45 +40095,448 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>2</v>
+      </c>
+      <c r="O221" t="n">
+        <v>2</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV220" t="inlineStr">
+      <c r="AV221" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW220" t="inlineStr">
+      <c r="AW221" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX220" t="inlineStr">
+      <c r="AX221" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY220" t="inlineStr">
+      <c r="AY221" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ220" t="inlineStr">
+      <c r="AZ221" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA220" t="inlineStr">
+      <c r="BA221" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB220" t="inlineStr">
+      <c r="BB221" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC220" t="inlineStr">
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" t="n">
+        <v>2</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -40255,7 +40658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -40265,7 +40668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
@@ -40285,7 +40688,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -40317,7 +40720,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35178</v>
+        <v>35389</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="O160" t="n">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="R160" t="n">
-        <v>2.666461380971368</v>
+        <v>2.677479816429927</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -34867,13 +34867,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="O190" t="n">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="R190" t="n">
-        <v>2.321217069936508</v>
+        <v>2.361617999951225</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -36148,13 +36148,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O199" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="R199" t="n">
-        <v>0.8716164937234273</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36312,10 +36312,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O200" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -39803,13 +39803,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R219" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -39967,10 +39967,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35389</v>
+        <v>35408</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -34867,13 +34867,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="O190" t="n">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="R190" t="n">
-        <v>2.361617999951225</v>
+        <v>2.394673306326903</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -36148,13 +36148,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O199" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R199" t="n">
-        <v>0.9249807688493514</v>
+        <v>0.9427688605579929</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -36312,10 +36312,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O200" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -36551,13 +36551,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O201" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R201" t="n">
-        <v>2.052011957922787</v>
+        <v>2.140460749212563</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -36715,10 +36715,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O202" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -39803,13 +39803,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O219" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R219" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -39967,10 +39967,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O220" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
@@ -40206,13 +40206,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R221" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40370,10 +40370,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35408</v>
+        <v>35441</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O160" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="R160" t="n">
-        <v>2.677479816429927</v>
+        <v>2.681152628249447</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -34867,13 +34867,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="O190" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="R190" t="n">
-        <v>2.394673306326903</v>
+        <v>2.405691741785462</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -39619,12 +39619,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39649,90 +39649,102 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N218" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O218" t="n">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="P218" t="n">
+        <v>13</v>
       </c>
       <c r="R218" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.2201245481626162</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39759,17 +39771,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39794,37 +39806,115 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O219" t="n">
-        <v>7</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0.1245166419604896</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="P219" t="n">
+        <v>13</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -39833,22 +39923,17 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -39856,47 +39941,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39923,17 +40008,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39967,175 +40052,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="O220" t="n">
-        <v>7</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.09549310730751455</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP220" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT220" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV220" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40167,12 +40158,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40206,13 +40197,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O221" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R221" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40221,7 +40212,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -40241,7 +40232,7 @@
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
@@ -40251,7 +40242,7 @@
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -40259,47 +40250,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40331,12 +40322,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40370,29 +40361,29 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O222" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -40417,7 +40408,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -40452,17 +40443,17 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -40480,7 +40471,7 @@
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -40490,7 +40481,7 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -40498,47 +40489,595 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>18</v>
+      </c>
+      <c r="O223" t="n">
+        <v>18</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV222" t="inlineStr">
+      <c r="AV223" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW222" t="inlineStr">
+      <c r="AW223" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX222" t="inlineStr">
+      <c r="AX223" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY222" t="inlineStr">
+      <c r="AY223" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ222" t="inlineStr">
+      <c r="AZ223" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA222" t="inlineStr">
+      <c r="BA223" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB222" t="inlineStr">
+      <c r="BB223" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC222" t="inlineStr">
+      <c r="BC223" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>18</v>
+      </c>
+      <c r="O224" t="n">
+        <v>18</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>873</v>
+      </c>
+      <c r="O225" t="n">
+        <v>873</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.2501178289907673</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40575,7 +41114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -40658,7 +41197,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -40668,7 +41207,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -40688,7 +41227,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -40720,7 +41259,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35441</v>
+        <v>36335</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -14971,10 +14971,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O79" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -19265,10 +19265,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O102" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -19421,10 +19421,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O103" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -25390,10 +25390,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="O137" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -25546,10 +25546,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="O138" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -30925,12 +30925,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -30964,81 +30964,92 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="O169" t="n">
-        <v>290</v>
-      </c>
-      <c r="R169" t="n">
-        <v>3.219432762590813</v>
+        <v>243</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31065,17 +31076,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -31109,22 +31120,39 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="O170" t="n">
-        <v>67</v>
-      </c>
-      <c r="R170" t="n">
-        <v>1.191802144478972</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>243</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -31132,6 +31160,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary salmonellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -31139,70 +31225,65 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_CA_ON_PHO_IDTO_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31229,17 +31310,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -31273,175 +31354,81 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>67</v>
+        <v>290</v>
       </c>
       <c r="O171" t="n">
-        <v>67</v>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>1</v>
+        <v>290</v>
+      </c>
+      <c r="R171" t="n">
+        <v>3.219432762590813</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -31473,12 +31460,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -31512,13 +31499,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="O172" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="R172" t="n">
-        <v>1.963563166633012</v>
+        <v>1.191802144478972</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -31527,7 +31514,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -31547,7 +31534,7 @@
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
@@ -31557,7 +31544,7 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT172" t="n">
@@ -31565,47 +31552,47 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31637,12 +31624,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -31676,29 +31663,29 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="O173" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -31723,7 +31710,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -31758,17 +31745,17 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -31786,7 +31773,7 @@
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
@@ -31796,7 +31783,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -31804,47 +31791,47 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31876,12 +31863,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -31915,13 +31902,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="O174" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="R174" t="n">
-        <v>1.361707535859717</v>
+        <v>1.963563166633012</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -31930,7 +31917,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -31945,7 +31932,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -31953,57 +31940,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32035,12 +32027,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -32074,29 +32066,29 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="O175" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Salmonellose</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -32106,7 +32098,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -32121,7 +32113,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -32156,17 +32148,17 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -32179,7 +32171,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -32187,57 +32179,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32269,12 +32266,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -32308,13 +32305,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="O176" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="R176" t="n">
-        <v>1.326973020816235</v>
+        <v>1.361707535859717</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -32323,7 +32320,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -32338,7 +32335,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -32346,62 +32343,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32433,12 +32425,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -32472,29 +32464,29 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="O177" t="n">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>Salmonellainfektion</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -32504,7 +32496,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -32519,7 +32511,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -32554,17 +32546,17 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -32577,7 +32569,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -32585,62 +32577,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32672,12 +32659,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32702,7 +32689,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -32711,81 +32698,100 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="O178" t="n">
-        <v>671</v>
+        <v>142</v>
       </c>
       <c r="R178" t="n">
-        <v>0.1922440587088257</v>
+        <v>1.326973020816235</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32812,17 +32818,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -32847,7 +32853,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -32856,26 +32862,103 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="O179" t="n">
-        <v>36</v>
-      </c>
-      <c r="P179" t="n">
-        <v>36</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0.6095756718349371</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>142</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -32884,7 +32967,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -32892,9 +32975,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -32902,47 +32990,47 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32969,17 +33057,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33004,7 +33092,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -33013,173 +33101,81 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>36</v>
+        <v>671</v>
       </c>
       <c r="O180" t="n">
-        <v>36</v>
-      </c>
-      <c r="P180" t="n">
-        <v>36</v>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
+        <v>671</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.1922440587088257</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33211,12 +33207,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33241,7 +33237,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -33250,81 +33246,93 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>839</v>
+        <v>36</v>
       </c>
       <c r="O181" t="n">
-        <v>839</v>
+        <v>36</v>
+      </c>
+      <c r="P181" t="n">
+        <v>36</v>
       </c>
       <c r="R181" t="n">
-        <v>0.2403766993393514</v>
+        <v>0.6095756718349371</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33351,7 +33359,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -33386,7 +33394,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -33395,26 +33403,106 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="O182" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P182" t="n">
-        <v>20</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0.3386531510194095</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>36</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -33508,17 +33596,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33543,7 +33631,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -33552,173 +33640,81 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>20</v>
+        <v>839</v>
       </c>
       <c r="O183" t="n">
-        <v>20</v>
-      </c>
-      <c r="P183" t="n">
-        <v>20</v>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
+        <v>839</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.2403766993393514</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33750,12 +33746,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33780,7 +33776,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -33789,81 +33785,93 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1110</v>
+        <v>20</v>
       </c>
       <c r="O184" t="n">
-        <v>1110</v>
+        <v>20</v>
+      </c>
+      <c r="P184" t="n">
+        <v>20</v>
       </c>
       <c r="R184" t="n">
-        <v>0.3180192327374018</v>
+        <v>0.3386531510194095</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33890,7 +33898,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -33925,7 +33933,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -33934,26 +33942,106 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O185" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P185" t="n">
-        <v>22</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0.3725184661213504</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>20</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -34047,17 +34135,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34082,7 +34170,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -34091,173 +34179,81 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>22</v>
+        <v>1110</v>
       </c>
       <c r="O186" t="n">
-        <v>22</v>
-      </c>
-      <c r="P186" t="n">
-        <v>22</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
+        <v>1110</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.3180192327374018</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34289,12 +34285,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34319,7 +34315,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -34328,81 +34324,93 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1115</v>
+        <v>22</v>
       </c>
       <c r="O187" t="n">
-        <v>1115</v>
+        <v>22</v>
+      </c>
+      <c r="P187" t="n">
+        <v>22</v>
       </c>
       <c r="R187" t="n">
-        <v>0.3194517518037865</v>
+        <v>0.3725184661213504</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34429,7 +34437,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -34464,7 +34472,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34473,26 +34481,106 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O188" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="P188" t="n">
-        <v>30</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0.5079797265291142</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>22</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -34586,17 +34674,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34621,7 +34709,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -34630,173 +34718,81 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>30</v>
+        <v>1115</v>
       </c>
       <c r="O189" t="n">
-        <v>30</v>
-      </c>
-      <c r="P189" t="n">
-        <v>30</v>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
+        <v>1115</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.3194517518037865</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34828,12 +34824,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34858,90 +34854,102 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N190" t="n">
-        <v>655</v>
+        <v>30</v>
       </c>
       <c r="O190" t="n">
-        <v>655</v>
+        <v>30</v>
+      </c>
+      <c r="P190" t="n">
+        <v>30</v>
       </c>
       <c r="R190" t="n">
-        <v>2.405691741785462</v>
+        <v>0.5079797265291142</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34968,17 +34976,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35003,87 +35011,182 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O191" t="n">
-        <v>11</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="P191" t="n">
+        <v>30</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35115,12 +35218,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35154,14 +35257,17 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>147</v>
+        <v>655</v>
       </c>
       <c r="O192" t="n">
-        <v>147</v>
+        <v>655</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.405691741785462</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -35195,12 +35301,12 @@
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -35215,12 +35321,12 @@
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
@@ -35257,12 +35363,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35296,10 +35402,10 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O193" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -35337,7 +35443,7 @@
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
@@ -35357,7 +35463,7 @@
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
@@ -35399,12 +35505,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35438,10 +35544,10 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="O194" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -35479,7 +35585,7 @@
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
@@ -35499,7 +35605,7 @@
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
@@ -35541,12 +35647,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35580,10 +35686,10 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="O195" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -35621,7 +35727,7 @@
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
@@ -35641,7 +35747,7 @@
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
@@ -35683,12 +35789,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -35722,10 +35828,10 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="O196" t="n">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -35763,7 +35869,7 @@
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
@@ -35783,7 +35889,7 @@
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
@@ -35825,12 +35931,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35864,10 +35970,10 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="O197" t="n">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -35905,7 +36011,7 @@
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
@@ -35925,7 +36031,7 @@
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
@@ -35967,12 +36073,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36006,10 +36112,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="O198" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -36047,7 +36153,7 @@
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
@@ -36067,7 +36173,7 @@
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
@@ -36109,12 +36215,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36148,100 +36254,78 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="O199" t="n">
-        <v>53</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.9427688605579929</v>
+        <v>103</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36268,17 +36352,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36312,175 +36396,78 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="O200" t="n">
-        <v>53</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT200" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV200" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36512,12 +36499,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -36551,100 +36538,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>121</v>
+        <v>555</v>
       </c>
       <c r="O201" t="n">
-        <v>121</v>
+        <v>555</v>
       </c>
       <c r="R201" t="n">
-        <v>2.140460749212563</v>
+        <v>6.161328218061729</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -36671,17 +36639,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -36715,39 +36683,22 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="O202" t="n">
-        <v>121</v>
+        <v>53</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.9427688605579929</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Salmonellose</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -36755,64 +36706,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36825,7 +36718,7 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -36835,7 +36728,7 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -36843,47 +36736,47 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36910,17 +36803,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36954,22 +36847,39 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>209</v>
+        <v>53</v>
       </c>
       <c r="O203" t="n">
-        <v>209</v>
-      </c>
-      <c r="R203" t="n">
-        <v>1.953080009511219</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>53</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Salmonella, other</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -36977,6 +36887,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36989,7 +36957,7 @@
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
@@ -36999,7 +36967,7 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -37007,47 +36975,47 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37074,17 +37042,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37118,39 +37086,22 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="O204" t="n">
-        <v>209</v>
+        <v>121</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.140460749212563</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Salmonellainfektion</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -37158,64 +37109,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37238,7 +37131,7 @@
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NO_FHI_302_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
@@ -37251,42 +37144,42 @@
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37313,17 +37206,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37357,81 +37250,175 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1166</v>
+        <v>121</v>
       </c>
       <c r="O205" t="n">
-        <v>1166</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.3340634462809103</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>121</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37463,12 +37450,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37493,7 +37480,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -37502,25 +37489,27 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="O206" t="n">
-        <v>25</v>
-      </c>
-      <c r="P206" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="R206" t="n">
-        <v>0.4233164387742618</v>
+        <v>1.953080009511219</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -37530,7 +37519,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -37538,9 +37527,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -37548,47 +37542,47 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37620,12 +37614,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37650,7 +37644,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37659,32 +37653,29 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="O207" t="n">
-        <v>25</v>
-      </c>
-      <c r="P207" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
+          <t>Salmonellainfektion</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -37694,12 +37685,12 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
@@ -37709,7 +37700,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -37744,17 +37735,17 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -37767,7 +37758,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -37775,9 +37766,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT207" t="n">
@@ -37785,47 +37781,47 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37887,7 +37883,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -37896,13 +37892,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="O208" t="n">
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="R208" t="n">
-        <v>0.3036940420735548</v>
+        <v>0.3340634462809103</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -38032,7 +38028,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -38189,7 +38185,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -38426,7 +38422,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -38435,13 +38431,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="O211" t="n">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="R211" t="n">
-        <v>0.3025480268204471</v>
+        <v>0.3036940420735548</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38571,7 +38567,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -38580,16 +38576,16 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O212" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P212" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R212" t="n">
-        <v>0.4741144114271733</v>
+        <v>0.4233164387742618</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -38728,7 +38724,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -38737,13 +38733,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O213" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P213" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -38965,7 +38961,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -38974,13 +38970,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>993</v>
+        <v>1056</v>
       </c>
       <c r="O214" t="n">
-        <v>993</v>
+        <v>1056</v>
       </c>
       <c r="R214" t="n">
-        <v>0.2844982865839999</v>
+        <v>0.3025480268204471</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -39110,7 +39106,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39119,16 +39115,16 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O215" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P215" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R215" t="n">
-        <v>0.5079797265291142</v>
+        <v>0.4741144114271733</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -39267,7 +39263,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -39276,13 +39272,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O216" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P216" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -39504,7 +39500,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -39513,13 +39509,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1047</v>
+        <v>993</v>
       </c>
       <c r="O217" t="n">
-        <v>1047</v>
+        <v>993</v>
       </c>
       <c r="R217" t="n">
-        <v>0.2999694925009547</v>
+        <v>0.2844982865839999</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -39649,7 +39645,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -39658,16 +39654,16 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O218" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="P218" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R218" t="n">
-        <v>0.2201245481626162</v>
+        <v>0.5079797265291142</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -39806,7 +39802,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -39815,13 +39811,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O219" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="P219" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -40013,12 +40009,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -40043,22 +40039,22 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>26</v>
+        <v>1047</v>
       </c>
       <c r="O220" t="n">
-        <v>26</v>
+        <v>1047</v>
       </c>
       <c r="R220" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.2999694925009547</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -40091,42 +40087,42 @@
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40158,12 +40154,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40188,36 +40184,34 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N221" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O221" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="P221" t="n">
+        <v>13</v>
       </c>
       <c r="R221" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2201245481626162</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -40227,22 +40221,17 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -40250,47 +40239,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40322,12 +40311,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40352,38 +40341,41 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O222" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="P222" t="n">
+        <v>13</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>Salmonella, other</t>
+          <t>Salmonellosis (non-enteric fevers)</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -40393,12 +40385,12 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr">
@@ -40408,7 +40400,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -40443,12 +40435,12 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -40466,22 +40458,17 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -40489,47 +40476,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40561,12 +40548,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -40600,100 +40587,81 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O223" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="R223" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40720,17 +40688,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40764,39 +40732,22 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O224" t="n">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.1956690087950551</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Salmonellose</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -40804,64 +40755,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40874,7 +40767,7 @@
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
@@ -40884,7 +40777,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -40892,47 +40785,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40959,123 +40852,765 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>11</v>
+      </c>
+      <c r="O225" t="n">
+        <v>11</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Salmonella, other</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>18</v>
+      </c>
+      <c r="O226" t="n">
+        <v>18</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>18</v>
+      </c>
+      <c r="O227" t="n">
+        <v>18</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>D114</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>Salmonellosis</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>沙门氏菌病</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="K228" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N225" t="n">
+      <c r="N228" t="n">
         <v>873</v>
       </c>
-      <c r="O225" t="n">
+      <c r="O228" t="n">
         <v>873</v>
       </c>
-      <c r="R225" t="n">
+      <c r="R228" t="n">
         <v>0.2501178289907673</v>
       </c>
-      <c r="S225" t="inlineStr">
+      <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO225" t="inlineStr">
+      <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP225" t="inlineStr">
+      <c r="AP228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR225" t="inlineStr">
+      <c r="AR228" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS225" t="inlineStr"/>
-      <c r="AT225" t="n">
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
         <v>0</v>
       </c>
-      <c r="AU225" t="inlineStr">
+      <c r="AU228" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV225" t="inlineStr">
+      <c r="AV228" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW225" t="inlineStr">
+      <c r="AW228" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX225" t="inlineStr">
+      <c r="AX228" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY225" t="inlineStr">
+      <c r="AY228" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ225" t="inlineStr">
+      <c r="AZ228" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA225" t="inlineStr">
+      <c r="BA228" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB225" t="inlineStr">
+      <c r="BB228" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC225" t="inlineStr">
+      <c r="BC228" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -41197,7 +41732,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -41207,7 +41742,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -41227,7 +41762,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -41259,7 +41794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36335</v>
+        <v>37145</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O160" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="R160" t="n">
-        <v>2.681152628249447</v>
+        <v>2.684825440068967</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O192" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="R192" t="n">
-        <v>2.405691741785462</v>
+        <v>2.413037365424502</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -40732,13 +40732,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R224" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -40896,10 +40896,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O225" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37145</v>
+        <v>37149</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O160" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="R160" t="n">
-        <v>2.684825440068967</v>
+        <v>2.688498251888487</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O192" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="R192" t="n">
-        <v>2.413037365424502</v>
+        <v>2.420382989063542</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37149</v>
+        <v>37152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="O192" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R192" t="n">
-        <v>2.420382989063542</v>
+        <v>2.416710177244022</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -40732,13 +40732,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O224" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R224" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -40896,10 +40896,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O225" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37152</v>
+        <v>37158</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -37450,12 +37450,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37489,13 +37489,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="O206" t="n">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="R206" t="n">
-        <v>1.953080009511219</v>
+        <v>1.172581489212534</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -37527,62 +37527,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37614,12 +37609,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37653,29 +37648,29 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="O207" t="n">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>Salmonellainfektion</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -37685,7 +37680,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -37700,7 +37695,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -37735,17 +37730,17 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+          <t>New Zealand PHF Science monthly salmonellosis notifications.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -37758,7 +37753,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -37766,62 +37761,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+          <t>SER_NZ_SALMONELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37853,12 +37843,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37892,81 +37882,100 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1166</v>
+        <v>209</v>
       </c>
       <c r="O208" t="n">
-        <v>1166</v>
+        <v>209</v>
       </c>
       <c r="R208" t="n">
-        <v>0.3340634462809103</v>
+        <v>1.953080009511219</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37993,17 +38002,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38028,7 +38037,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -38037,26 +38046,103 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="O209" t="n">
-        <v>25</v>
-      </c>
-      <c r="P209" t="n">
-        <v>25</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.4233164387742618</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>209</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Salmonellainfektion</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Retain FHM source scope alongside separate Typhi and Paratyphi categories.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -38065,7 +38151,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -38073,9 +38159,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+          <t>SER_SE_FOHM_SMINET_SALMONELLA</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -38083,47 +38174,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -38150,17 +38241,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38185,7 +38276,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -38194,173 +38285,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>25</v>
+        <v>1166</v>
       </c>
       <c r="O210" t="n">
-        <v>25</v>
-      </c>
-      <c r="P210" t="n">
-        <v>25</v>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
+        <v>1166</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.3340634462809103</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38392,12 +38391,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38422,7 +38421,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -38431,81 +38430,93 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1060</v>
+        <v>25</v>
       </c>
       <c r="O211" t="n">
-        <v>1060</v>
+        <v>25</v>
+      </c>
+      <c r="P211" t="n">
+        <v>25</v>
       </c>
       <c r="R211" t="n">
-        <v>0.3036940420735548</v>
+        <v>0.4233164387742618</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38532,7 +38543,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -38567,7 +38578,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -38584,18 +38595,98 @@
       <c r="P212" t="n">
         <v>25</v>
       </c>
-      <c r="R212" t="n">
-        <v>0.4233164387742618</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -38689,17 +38780,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -38724,7 +38815,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -38733,173 +38824,81 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>25</v>
+        <v>1060</v>
       </c>
       <c r="O213" t="n">
-        <v>25</v>
-      </c>
-      <c r="P213" t="n">
-        <v>25</v>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
+        <v>1060</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.3036940420735548</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38931,12 +38930,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38961,7 +38960,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -38970,81 +38969,93 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1056</v>
+        <v>25</v>
       </c>
       <c r="O214" t="n">
-        <v>1056</v>
+        <v>25</v>
+      </c>
+      <c r="P214" t="n">
+        <v>25</v>
       </c>
       <c r="R214" t="n">
-        <v>0.3025480268204471</v>
+        <v>0.4233164387742618</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39071,7 +39082,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -39106,7 +39117,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39115,26 +39126,106 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O215" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P215" t="n">
-        <v>28</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.4741144114271733</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>25</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
@@ -39228,17 +39319,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39263,7 +39354,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -39272,173 +39363,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>28</v>
+        <v>1056</v>
       </c>
       <c r="O216" t="n">
-        <v>28</v>
-      </c>
-      <c r="P216" t="n">
-        <v>28</v>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
+        <v>1056</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.3025480268204471</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39470,12 +39469,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39500,7 +39499,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -39509,81 +39508,93 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>993</v>
+        <v>28</v>
       </c>
       <c r="O217" t="n">
-        <v>993</v>
+        <v>28</v>
+      </c>
+      <c r="P217" t="n">
+        <v>28</v>
       </c>
       <c r="R217" t="n">
-        <v>0.2844982865839999</v>
+        <v>0.4741144114271733</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39610,7 +39621,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -39645,7 +39656,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -39654,26 +39665,106 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O218" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P218" t="n">
-        <v>30</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0.5079797265291142</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>28</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -39767,17 +39858,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39802,7 +39893,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -39811,173 +39902,81 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>30</v>
+        <v>993</v>
       </c>
       <c r="O219" t="n">
-        <v>30</v>
-      </c>
-      <c r="P219" t="n">
-        <v>30</v>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
+        <v>993</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.2844982865839999</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40009,12 +40008,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -40039,7 +40038,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -40048,81 +40047,93 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1047</v>
+        <v>30</v>
       </c>
       <c r="O220" t="n">
-        <v>1047</v>
+        <v>30</v>
+      </c>
+      <c r="P220" t="n">
+        <v>30</v>
       </c>
       <c r="R220" t="n">
-        <v>0.2999694925009547</v>
+        <v>0.5079797265291142</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40160,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -40184,7 +40195,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -40193,26 +40204,106 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O221" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="P221" t="n">
-        <v>13</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0.2201245481626162</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>30</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -40306,17 +40397,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40341,7 +40432,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -40350,173 +40441,81 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>13</v>
+        <v>1047</v>
       </c>
       <c r="O222" t="n">
-        <v>13</v>
-      </c>
-      <c r="P222" t="n">
-        <v>13</v>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Salmonellosis (non-enteric fevers)</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
+        <v>1047</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.2999694925009547</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40548,12 +40547,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -40578,90 +40577,102 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O223" t="n">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="P223" t="n">
+        <v>13</v>
       </c>
       <c r="R223" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.2201245481626162</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40688,17 +40699,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40723,37 +40734,115 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N224" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O224" t="n">
-        <v>19</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.3379737424641861</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="P224" t="n">
+        <v>13</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -40762,22 +40851,17 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1200</t>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -40785,47 +40869,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40852,17 +40936,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40896,175 +40980,81 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O225" t="n">
-        <v>19</v>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Salmonella, other</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.09549310730751455</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP225" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1200</t>
-        </is>
-      </c>
-      <c r="AT225" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV225" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41096,12 +41086,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -41135,13 +41125,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O226" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R226" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41150,7 +41140,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -41170,7 +41160,7 @@
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
@@ -41180,7 +41170,7 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -41188,47 +41178,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41260,12 +41250,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41299,29 +41289,29 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O227" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>Salmonellose</t>
+          <t>Salmonella, other</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -41346,7 +41336,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -41381,17 +41371,17 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -41409,7 +41399,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
@@ -41419,7 +41409,7 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_302_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1200</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -41427,47 +41417,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41499,118 +41489,521 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>18</v>
+      </c>
+      <c r="O228" t="n">
+        <v>18</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>18</v>
+      </c>
+      <c r="O229" t="n">
+        <v>18</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Salmonellose</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_302_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>D114</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>Salmonellosis</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>沙门氏菌病</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="K230" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N228" t="n">
+      <c r="N230" t="n">
         <v>873</v>
       </c>
-      <c r="O228" t="n">
+      <c r="O230" t="n">
         <v>873</v>
       </c>
-      <c r="R228" t="n">
+      <c r="R230" t="n">
         <v>0.2501178289907673</v>
       </c>
-      <c r="S228" t="inlineStr">
+      <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO228" t="inlineStr">
+      <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP228" t="inlineStr">
+      <c r="AP230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR228" t="inlineStr">
+      <c r="AR230" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS228" t="inlineStr"/>
-      <c r="AT228" t="n">
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
         <v>0</v>
       </c>
-      <c r="AU228" t="inlineStr">
+      <c r="AU230" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV228" t="inlineStr">
+      <c r="AV230" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW228" t="inlineStr">
+      <c r="AW230" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX228" t="inlineStr">
+      <c r="AX230" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY228" t="inlineStr">
+      <c r="AY230" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ228" t="inlineStr">
+      <c r="AZ230" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA228" t="inlineStr">
+      <c r="BA230" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB228" t="inlineStr">
+      <c r="BB230" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC228" t="inlineStr">
+      <c r="BC230" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -41732,7 +42125,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -41742,7 +42135,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -41762,7 +42155,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -41794,7 +42187,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37158</v>
+        <v>37220</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -37086,13 +37086,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O204" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R204" t="n">
-        <v>2.140460749212563</v>
+        <v>2.122770990954607</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -37250,10 +37250,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O205" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
@@ -41528,13 +41528,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="O228" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="R228" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.6368312972863822</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41692,10 +41692,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="O229" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37220</v>
+        <v>37237</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -36683,13 +36683,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O202" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R202" t="n">
-        <v>0.9427688605579929</v>
+        <v>0.9605569522666343</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -36847,10 +36847,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O203" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -41125,13 +41125,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O226" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R226" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41289,10 +41289,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O227" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37237</v>
+        <v>37242</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -28750,16 +28750,16 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O155" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P155" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R155" t="n">
-        <v>0.4402490963252323</v>
+        <v>0.4741144114271733</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -28907,13 +28907,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O156" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P156" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -29289,16 +29289,16 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O158" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P158" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R158" t="n">
-        <v>0.5418450416310552</v>
+        <v>0.5587776991820257</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -29446,13 +29446,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O159" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P159" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O160" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="R160" t="n">
-        <v>2.688498251888487</v>
+        <v>2.692171063708006</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -33246,16 +33246,16 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O181" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P181" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R181" t="n">
-        <v>0.6095756718349371</v>
+        <v>0.643440986936878</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -33403,13 +33403,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O182" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P182" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -34324,16 +34324,16 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O187" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P187" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R187" t="n">
-        <v>0.3725184661213504</v>
+        <v>0.3386531510194095</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -34481,13 +34481,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O188" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P188" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
@@ -34863,16 +34863,16 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O190" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P190" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R190" t="n">
-        <v>0.5079797265291142</v>
+        <v>0.5249123840800847</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -35020,13 +35020,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O191" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P191" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="O192" t="n">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="R192" t="n">
-        <v>2.416710177244022</v>
+        <v>2.460783919078259</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -38430,16 +38430,16 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O211" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P211" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R211" t="n">
-        <v>0.4233164387742618</v>
+        <v>0.4571817538762028</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38587,13 +38587,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O212" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P212" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -40047,16 +40047,16 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O220" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P220" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R220" t="n">
-        <v>0.5079797265291142</v>
+        <v>0.5418450416310552</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -40204,13 +40204,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O221" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P221" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -40586,16 +40586,16 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O223" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P223" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R223" t="n">
-        <v>0.2201245481626162</v>
+        <v>0.2539898632645571</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -40743,13 +40743,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O224" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P224" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -42004,6 +42004,545 @@
         </is>
       </c>
       <c r="BC230" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>36</v>
+      </c>
+      <c r="O231" t="n">
+        <v>36</v>
+      </c>
+      <c r="P231" t="n">
+        <v>36</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.6095756718349371</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>36</v>
+      </c>
+      <c r="O232" t="n">
+        <v>36</v>
+      </c>
+      <c r="P232" t="n">
+        <v>36</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>852</v>
+      </c>
+      <c r="O233" t="n">
+        <v>852</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.2441012489119516</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -42042,7 +42581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -42125,7 +42664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -42135,7 +42674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -42155,7 +42694,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -42187,7 +42726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37242</v>
+        <v>38153</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O192" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="R192" t="n">
-        <v>2.460783919078259</v>
+        <v>2.468129542717299</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38153</v>
+        <v>38155</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -29683,13 +29683,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O160" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="R160" t="n">
-        <v>2.692171063708006</v>
+        <v>2.695843875527526</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="O192" t="n">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="R192" t="n">
-        <v>2.468129542717299</v>
+        <v>2.479147978175858</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -41125,13 +41125,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="O226" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="R226" t="n">
-        <v>0.4091261092987516</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41289,10 +41289,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="O227" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -41528,13 +41528,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="O228" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="R228" t="n">
-        <v>0.6368312972863822</v>
+        <v>1.061385495477304</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41692,10 +41692,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="O229" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -42543,6 +42543,545 @@
         </is>
       </c>
       <c r="BC233" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>22</v>
+      </c>
+      <c r="O234" t="n">
+        <v>22</v>
+      </c>
+      <c r="P234" t="n">
+        <v>22</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.3725184661213504</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>22</v>
+      </c>
+      <c r="O235" t="n">
+        <v>22</v>
+      </c>
+      <c r="P235" t="n">
+        <v>22</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>941</v>
+      </c>
+      <c r="O236" t="n">
+        <v>941</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.2696000882935992</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -42581,7 +43120,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -42664,7 +43203,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -42674,7 +43213,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -42694,7 +43233,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -42726,7 +43265,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38155</v>
+        <v>39164</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -35257,13 +35257,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="O192" t="n">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="R192" t="n">
-        <v>2.479147978175858</v>
+        <v>2.493839225453937</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -37882,13 +37882,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O208" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R208" t="n">
-        <v>1.953080009511219</v>
+        <v>1.943735129082936</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -38046,10 +38046,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O209" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -40980,13 +40980,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>26</v>
+        <v>698</v>
       </c>
       <c r="O225" t="n">
-        <v>26</v>
+        <v>698</v>
       </c>
       <c r="R225" t="n">
-        <v>0.09549310730751455</v>
+        <v>2.563622650024814</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -41125,13 +41125,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="O226" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="R226" t="n">
-        <v>0.7293117600542963</v>
+        <v>0.9783450439752756</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41289,10 +41289,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="O227" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -42076,16 +42076,16 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O231" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P231" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R231" t="n">
-        <v>0.6095756718349371</v>
+        <v>0.6265083293859075</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -42233,13 +42233,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O232" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P232" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
@@ -42615,16 +42615,16 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O234" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P234" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R234" t="n">
-        <v>0.3725184661213504</v>
+        <v>0.4571817538762028</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -42772,13 +42772,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O235" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P235" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -43084,6 +43084,948 @@
       <c r="BC236" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>24</v>
+      </c>
+      <c r="O237" t="n">
+        <v>24</v>
+      </c>
+      <c r="P237" t="n">
+        <v>24</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.4063837812232914</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>24</v>
+      </c>
+      <c r="O238" t="n">
+        <v>24</v>
+      </c>
+      <c r="P238" t="n">
+        <v>24</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Salmonellosis (non-enteric fevers)</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_SALMONELLOSIS_NON_ENTERIC_FEVERS; SER_SG_HIST_SALMONELLOSIS_NON_ENTERIC_FEVERS</t>
+        </is>
+      </c>
+      <c r="AT238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>913</v>
+      </c>
+      <c r="O239" t="n">
+        <v>913</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0.2615779815218449</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
+      <c r="AT239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="AT240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Salmonella, other</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Residual Salmonella category excluding Typhi and Paratyphi; retain as its own non-additive series.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1200</t>
+        </is>
+      </c>
+      <c r="AT241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43120,7 +44062,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -43203,7 +44145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -43213,7 +44155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -43233,7 +44175,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -43265,7 +44207,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39164</v>
+        <v>40796</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -40980,13 +40980,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="O225" t="n">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="R225" t="n">
-        <v>2.563622650024814</v>
+        <v>2.662788569151848</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40796</v>
+        <v>40823</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -26584,7 +26584,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -37342,7 +37342,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41125,13 +41125,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O226" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R226" t="n">
-        <v>0.9783450439752756</v>
+        <v>1.0317093191012</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41289,10 +41289,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O227" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -41528,13 +41528,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O228" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="R228" t="n">
-        <v>1.061385495477304</v>
+        <v>1.379801144120495</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41692,10 +41692,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O229" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -43693,13 +43693,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -43857,10 +43857,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40823</v>
+        <v>40845</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -47817,13 +47817,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="O267" t="n">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="R267" t="n">
-        <v>2.736244805542244</v>
+        <v>2.758281676459362</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -52552,13 +52552,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O294" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R294" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -52716,10 +52716,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O295" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U295" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49545</v>
+        <v>49555</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -47817,13 +47817,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="O267" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="R267" t="n">
-        <v>2.758281676459362</v>
+        <v>2.776645735556961</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -49570,13 +49570,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O278" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R278" t="n">
-        <v>1.415180660636405</v>
+        <v>1.43287041889436</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -49734,10 +49734,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O279" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
@@ -49973,13 +49973,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O280" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R280" t="n">
-        <v>1.383042303385935</v>
+        <v>1.373697422957652</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -50137,10 +50137,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O281" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
@@ -52552,13 +52552,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O294" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R294" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -52716,10 +52716,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O295" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="U295" t="inlineStr">
         <is>
@@ -52955,13 +52955,13 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="O296" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="R296" t="n">
-        <v>0.283036132127281</v>
+        <v>0.548382505996607</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -53119,10 +53119,10 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="O297" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="U297" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49555</v>
+        <v>49587</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d114/2026-2029.xlsx
+++ b/diseases/d114/2026-2029.xlsx
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O20" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9531778036849013</v>
+        <v>0.9438329232566179</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O21" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4258,16 +4258,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01060064109124673</v>
+        <v>0.01031413727796979</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4810,9 +4807,6 @@
       <c r="O25" t="n">
         <v>337</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.09655178507432829</v>
       </c>
@@ -5352,16 +5346,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O28" t="n">
-        <v>314</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0899621973689587</v>
+        <v>0.08938918974240483</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5899,16 +5890,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O31" t="n">
-        <v>328</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="R31" t="n">
-        <v>0.09397325075483584</v>
+        <v>0.0936867469415589</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -6446,16 +6434,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O34" t="n">
-        <v>286</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="R34" t="n">
-        <v>0.08194009059720443</v>
+        <v>0.08165358678392748</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -9694,13 +9679,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O53" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R53" t="n">
-        <v>0.8130045972606511</v>
+        <v>0.8036597168323677</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -9858,10 +9843,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O54" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -10496,9 +10481,6 @@
       <c r="O57" t="n">
         <v>321</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.09196772406189727</v>
       </c>
@@ -11043,9 +11025,6 @@
       <c r="O60" t="n">
         <v>258</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.07391798382545015</v>
       </c>
@@ -11585,16 +11564,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O63" t="n">
-        <v>262</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0750639990785579</v>
+        <v>0.07420448763872707</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -12132,16 +12108,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O66" t="n">
-        <v>341</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="R66" t="n">
-        <v>0.09769780032743604</v>
+        <v>0.09741129651415908</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -16177,16 +16150,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="O89" t="n">
-        <v>352</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="R89" t="n">
-        <v>0.1008493422734824</v>
+        <v>0.1002763346469285</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16724,16 +16694,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O92" t="n">
-        <v>302</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="R92" t="n">
-        <v>0.08652415160963543</v>
+        <v>0.08623764779635849</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -17276,9 +17243,6 @@
       <c r="O95" t="n">
         <v>296</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.08480512872997381</v>
       </c>
@@ -17818,16 +17782,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O98" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="R98" t="n">
-        <v>0.1040008842195287</v>
+        <v>0.1037143804062517</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -21862,9 +21823,6 @@
       <c r="O121" t="n">
         <v>385</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.1103039681116213</v>
       </c>
@@ -22409,9 +22367,6 @@
       <c r="O124" t="n">
         <v>415</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.1188990825099295</v>
       </c>
@@ -22951,16 +22906,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="O127" t="n">
-        <v>395</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="R127" t="n">
-        <v>0.1131690062443907</v>
+        <v>0.1123094948045599</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -23498,16 +23450,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O130" t="n">
-        <v>427</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="R130" t="n">
-        <v>0.1223371282692528</v>
+        <v>0.1220506244559758</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -27542,9 +27491,6 @@
       <c r="O153" t="n">
         <v>488</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.139813860879146</v>
       </c>
@@ -28084,16 +28030,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O156" t="n">
-        <v>478</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1369488227463766</v>
+        <v>0.1366623189330997</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -28636,9 +28579,6 @@
       <c r="O159" t="n">
         <v>507</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.1452574333314078</v>
       </c>
@@ -29178,16 +29118,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O162" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="R162" t="n">
-        <v>0.03953752623221752</v>
+        <v>0.03925102241894058</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -53436,6 +53373,156 @@
         </is>
       </c>
       <c r="BC298" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>salmonellosis</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>834</v>
+      </c>
+      <c r="O299" t="n">
+        <v>834</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0.2389441802729667</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr"/>
+      <c r="AT299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV299" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA299" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB299" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC299" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -53474,7 +53561,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -53557,7 +53644,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -53567,7 +53654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11">
@@ -53619,7 +53706,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49587</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="16">
